--- a/data/review/gpt-5.4-pro/step-4-answers-review.xlsx
+++ b/data/review/gpt-5.4-pro/step-4-answers-review.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O176"/>
+  <dimension ref="A1:P176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -438,6 +438,7 @@
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,6 +517,11 @@
           <t>Agreement</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Reviewer</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -608,6 +614,7 @@
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -700,6 +707,7 @@
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -792,6 +800,7 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -884,6 +893,7 @@
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -976,6 +986,7 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1068,6 +1079,7 @@
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1160,6 +1172,7 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1252,6 +1265,7 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1344,6 +1358,7 @@
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1436,6 +1451,7 @@
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1528,6 +1544,7 @@
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1620,6 +1637,7 @@
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1712,6 +1730,7 @@
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1804,6 +1823,7 @@
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1896,6 +1916,7 @@
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1988,6 +2009,7 @@
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2080,6 +2102,7 @@
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2172,6 +2195,7 @@
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2264,6 +2288,7 @@
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2356,6 +2381,7 @@
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2448,6 +2474,7 @@
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2540,6 +2567,7 @@
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2632,6 +2660,7 @@
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2724,6 +2753,7 @@
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2816,6 +2846,7 @@
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2908,6 +2939,7 @@
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3000,6 +3032,7 @@
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3092,6 +3125,7 @@
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3184,6 +3218,7 @@
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3276,6 +3311,7 @@
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3368,6 +3404,7 @@
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3460,6 +3497,7 @@
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3552,6 +3590,7 @@
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3644,6 +3683,7 @@
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3736,6 +3776,7 @@
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3828,6 +3869,7 @@
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3920,6 +3962,7 @@
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4012,6 +4055,7 @@
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4104,6 +4148,7 @@
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4196,6 +4241,7 @@
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4288,6 +4334,7 @@
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4380,6 +4427,7 @@
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4472,6 +4520,7 @@
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4564,6 +4613,7 @@
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4656,6 +4706,7 @@
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4751,6 +4802,7 @@
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4843,6 +4895,7 @@
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4935,6 +4988,7 @@
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5027,6 +5081,7 @@
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5119,6 +5174,7 @@
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5211,6 +5267,7 @@
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5303,6 +5360,7 @@
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5395,6 +5453,7 @@
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5487,6 +5546,7 @@
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5579,6 +5639,7 @@
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5671,6 +5732,7 @@
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5763,6 +5825,7 @@
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5855,6 +5918,7 @@
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5947,6 +6011,7 @@
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6039,6 +6104,7 @@
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6131,6 +6197,7 @@
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6223,6 +6290,7 @@
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6315,6 +6383,7 @@
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6407,6 +6476,7 @@
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6499,6 +6569,7 @@
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6591,6 +6662,7 @@
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6683,6 +6755,7 @@
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6775,6 +6848,7 @@
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6867,6 +6941,7 @@
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6959,6 +7034,7 @@
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7051,6 +7127,7 @@
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7143,6 +7220,7 @@
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7235,6 +7313,7 @@
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7327,6 +7406,7 @@
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7419,6 +7499,7 @@
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7511,6 +7592,7 @@
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7603,6 +7685,7 @@
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7695,6 +7778,7 @@
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7787,6 +7871,7 @@
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7879,6 +7964,7 @@
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7971,6 +8057,7 @@
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8063,6 +8150,7 @@
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8155,6 +8243,7 @@
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8247,6 +8336,7 @@
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8339,6 +8429,7 @@
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8431,6 +8522,7 @@
         </is>
       </c>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8523,6 +8615,7 @@
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8615,6 +8708,7 @@
         </is>
       </c>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8707,6 +8801,7 @@
         </is>
       </c>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8799,6 +8894,7 @@
         </is>
       </c>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8891,6 +8987,7 @@
         </is>
       </c>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8983,6 +9080,7 @@
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9075,6 +9173,7 @@
         </is>
       </c>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9167,6 +9266,7 @@
         </is>
       </c>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9259,6 +9359,7 @@
         </is>
       </c>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9351,6 +9452,7 @@
         </is>
       </c>
       <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9443,6 +9545,7 @@
         </is>
       </c>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9535,6 +9638,7 @@
         </is>
       </c>
       <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9627,6 +9731,7 @@
         </is>
       </c>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9719,6 +9824,7 @@
         </is>
       </c>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9811,6 +9917,7 @@
         </is>
       </c>
       <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9903,6 +10010,7 @@
         </is>
       </c>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9995,6 +10103,7 @@
         </is>
       </c>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10087,6 +10196,7 @@
         </is>
       </c>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10179,6 +10289,7 @@
         </is>
       </c>
       <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10271,6 +10382,7 @@
         </is>
       </c>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10363,6 +10475,7 @@
         </is>
       </c>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10455,6 +10568,7 @@
         </is>
       </c>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10548,6 +10662,7 @@
         </is>
       </c>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10640,6 +10755,7 @@
         </is>
       </c>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10732,6 +10848,7 @@
         </is>
       </c>
       <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10824,6 +10941,7 @@
         </is>
       </c>
       <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10916,6 +11034,7 @@
         </is>
       </c>
       <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11008,6 +11127,7 @@
         </is>
       </c>
       <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11102,6 +11222,7 @@
         </is>
       </c>
       <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11194,6 +11315,7 @@
         </is>
       </c>
       <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11286,6 +11408,7 @@
         </is>
       </c>
       <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11378,6 +11501,7 @@
         </is>
       </c>
       <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11470,6 +11594,7 @@
         </is>
       </c>
       <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11562,6 +11687,7 @@
         </is>
       </c>
       <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11654,6 +11780,7 @@
         </is>
       </c>
       <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11746,6 +11873,7 @@
         </is>
       </c>
       <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11838,6 +11966,7 @@
         </is>
       </c>
       <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11931,6 +12060,7 @@
         </is>
       </c>
       <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12023,6 +12153,7 @@
         </is>
       </c>
       <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12115,6 +12246,7 @@
         </is>
       </c>
       <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12207,6 +12339,7 @@
         </is>
       </c>
       <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12299,6 +12432,7 @@
         </is>
       </c>
       <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12391,6 +12525,7 @@
         </is>
       </c>
       <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12483,6 +12618,7 @@
         </is>
       </c>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12578,6 +12714,7 @@
         </is>
       </c>
       <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12670,6 +12807,7 @@
         </is>
       </c>
       <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12762,6 +12900,7 @@
         </is>
       </c>
       <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12854,6 +12993,7 @@
         </is>
       </c>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12946,6 +13086,7 @@
         </is>
       </c>
       <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13038,6 +13179,7 @@
         </is>
       </c>
       <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13130,6 +13272,7 @@
         </is>
       </c>
       <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13222,6 +13365,7 @@
         </is>
       </c>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13314,6 +13458,7 @@
         </is>
       </c>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13406,6 +13551,7 @@
         </is>
       </c>
       <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13498,6 +13644,7 @@
         </is>
       </c>
       <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13590,6 +13737,7 @@
         </is>
       </c>
       <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13682,6 +13830,7 @@
         </is>
       </c>
       <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13774,6 +13923,7 @@
         </is>
       </c>
       <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13866,6 +14016,7 @@
         </is>
       </c>
       <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13958,6 +14109,7 @@
         </is>
       </c>
       <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14050,6 +14202,7 @@
         </is>
       </c>
       <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14142,6 +14295,7 @@
         </is>
       </c>
       <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14234,6 +14388,7 @@
         </is>
       </c>
       <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14326,6 +14481,7 @@
         </is>
       </c>
       <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14418,6 +14574,7 @@
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14510,6 +14667,7 @@
         </is>
       </c>
       <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14603,6 +14761,7 @@
         </is>
       </c>
       <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14695,6 +14854,7 @@
         </is>
       </c>
       <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14787,6 +14947,7 @@
         </is>
       </c>
       <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14879,6 +15040,7 @@
         </is>
       </c>
       <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14971,6 +15133,7 @@
         </is>
       </c>
       <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15063,6 +15226,7 @@
         </is>
       </c>
       <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15155,6 +15319,7 @@
         </is>
       </c>
       <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15247,6 +15412,7 @@
         </is>
       </c>
       <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15339,6 +15505,7 @@
         </is>
       </c>
       <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15431,6 +15598,7 @@
         </is>
       </c>
       <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15523,6 +15691,7 @@
         </is>
       </c>
       <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15615,6 +15784,7 @@
         </is>
       </c>
       <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15707,6 +15877,7 @@
         </is>
       </c>
       <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15799,6 +15970,7 @@
         </is>
       </c>
       <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15891,6 +16063,7 @@
         </is>
       </c>
       <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15983,6 +16156,7 @@
         </is>
       </c>
       <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16075,6 +16249,7 @@
         </is>
       </c>
       <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16167,6 +16342,7 @@
         </is>
       </c>
       <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16259,6 +16435,7 @@
         </is>
       </c>
       <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16351,6 +16528,7 @@
         </is>
       </c>
       <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16443,6 +16621,7 @@
         </is>
       </c>
       <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16535,6 +16714,7 @@
         </is>
       </c>
       <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16627,11 +16807,15 @@
         </is>
       </c>
       <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="O2:O176" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P176" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Reviewer A,Reviewer B"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
